--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/149.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/149.xlsx
@@ -426,13 +426,13 @@
         <v>-11.45066439146684</v>
       </c>
       <c r="E2">
-        <v>-17.61641353832839</v>
+        <v>-20.43932385201585</v>
       </c>
       <c r="F2">
-        <v>-5.296949944241792</v>
+        <v>-6.226524791213134</v>
       </c>
       <c r="G2">
-        <v>-15.16639556105109</v>
+        <v>-15.22402857713196</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.36643209804034</v>
       </c>
       <c r="E3">
-        <v>-17.80892802534247</v>
+        <v>-20.42049898556597</v>
       </c>
       <c r="F3">
-        <v>-5.772702052854618</v>
+        <v>-6.039126547147412</v>
       </c>
       <c r="G3">
-        <v>-15.10736802580746</v>
+        <v>-16.09072223678979</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.317192074414</v>
       </c>
       <c r="E4">
-        <v>-18.40823986093959</v>
+        <v>-21.86991407577899</v>
       </c>
       <c r="F4">
-        <v>-5.31569424183234</v>
+        <v>-5.90777978339212</v>
       </c>
       <c r="G4">
-        <v>-14.95294061433376</v>
+        <v>-16.83102652319937</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.30346776594345</v>
       </c>
       <c r="E5">
-        <v>-18.58298914442158</v>
+        <v>-21.80093183122015</v>
       </c>
       <c r="F5">
-        <v>-5.264784437991088</v>
+        <v>-6.009176923699196</v>
       </c>
       <c r="G5">
-        <v>-14.75967502387168</v>
+        <v>-15.07991076379803</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.29865591516694</v>
       </c>
       <c r="E6">
-        <v>-20.13983322351857</v>
+        <v>-23.3775245854646</v>
       </c>
       <c r="F6">
-        <v>-5.51574496960842</v>
+        <v>-5.949673636421302</v>
       </c>
       <c r="G6">
-        <v>-14.77390568177499</v>
+        <v>-15.11186822117624</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.28477117073511</v>
       </c>
       <c r="E7">
-        <v>-19.60127992368237</v>
+        <v>-23.06061291745981</v>
       </c>
       <c r="F7">
-        <v>-5.315368693443039</v>
+        <v>-6.160695262080059</v>
       </c>
       <c r="G7">
-        <v>-14.75329632916012</v>
+        <v>-15.47841840341415</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.23804979548096</v>
       </c>
       <c r="E8">
-        <v>-21.06807076866283</v>
+        <v>-24.87748650255124</v>
       </c>
       <c r="F8">
-        <v>-5.151848968130417</v>
+        <v>-6.255050451095937</v>
       </c>
       <c r="G8">
-        <v>-14.06621837827708</v>
+        <v>-15.86241484068362</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.13993611002194</v>
       </c>
       <c r="E9">
-        <v>-21.41088530799149</v>
+        <v>-24.75182134883839</v>
       </c>
       <c r="F9">
-        <v>-5.158496616537883</v>
+        <v>-6.293258897550064</v>
       </c>
       <c r="G9">
-        <v>-13.8278228664864</v>
+        <v>-15.2002872985386</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.97374702988778</v>
       </c>
       <c r="E10">
-        <v>-22.05908654897542</v>
+        <v>-25.20855418030401</v>
       </c>
       <c r="F10">
-        <v>-5.211590825220317</v>
+        <v>-5.922343310700738</v>
       </c>
       <c r="G10">
-        <v>-13.91875207834173</v>
+        <v>-14.68620847315571</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.72636611345926</v>
       </c>
       <c r="E11">
-        <v>-22.21723444674529</v>
+        <v>-25.67517267052837</v>
       </c>
       <c r="F11">
-        <v>-5.232310779066541</v>
+        <v>-6.047197330752888</v>
       </c>
       <c r="G11">
-        <v>-13.24631657866771</v>
+        <v>-14.59238850510651</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.40164440010371</v>
       </c>
       <c r="E12">
-        <v>-23.79943798028523</v>
+        <v>-27.17822753536225</v>
       </c>
       <c r="F12">
-        <v>-5.159509709871507</v>
+        <v>-6.191961161331323</v>
       </c>
       <c r="G12">
-        <v>-13.39403061083079</v>
+        <v>-14.80017186035835</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.00755152796892</v>
       </c>
       <c r="E13">
-        <v>-23.84671524892531</v>
+        <v>-25.9594612117819</v>
       </c>
       <c r="F13">
-        <v>-4.949589812858473</v>
+        <v>-5.453708534812765</v>
       </c>
       <c r="G13">
-        <v>-12.86395254912406</v>
+        <v>-13.35290377980471</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.575973126719994</v>
       </c>
       <c r="E14">
-        <v>-24.61970764813861</v>
+        <v>-27.77386677853915</v>
       </c>
       <c r="F14">
-        <v>-4.85397550539034</v>
+        <v>-4.614139947992605</v>
       </c>
       <c r="G14">
-        <v>-11.66934509109078</v>
+        <v>-13.26826795090039</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.136014436276147</v>
       </c>
       <c r="E15">
-        <v>-25.42453069115183</v>
+        <v>-28.4099226522345</v>
       </c>
       <c r="F15">
-        <v>-4.514387116980085</v>
+        <v>-4.823277866177396</v>
       </c>
       <c r="G15">
-        <v>-11.1920225096168</v>
+        <v>-13.55939761498369</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.72725269577966</v>
       </c>
       <c r="E16">
-        <v>-26.19700231585425</v>
+        <v>-28.88927068289442</v>
       </c>
       <c r="F16">
-        <v>-4.354851838874929</v>
+        <v>-5.045315121558581</v>
       </c>
       <c r="G16">
-        <v>-11.69715672502863</v>
+        <v>-12.40806946931949</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.377449207812251</v>
       </c>
       <c r="E17">
-        <v>-28.08677980399516</v>
+        <v>-29.99744714273346</v>
       </c>
       <c r="F17">
-        <v>-4.108836660652309</v>
+        <v>-4.803660469344298</v>
       </c>
       <c r="G17">
-        <v>-10.61490813685542</v>
+        <v>-12.67090187867413</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.112435072807047</v>
       </c>
       <c r="E18">
-        <v>-28.05581409873071</v>
+        <v>-30.57511740104792</v>
       </c>
       <c r="F18">
-        <v>-3.961613407254962</v>
+        <v>-4.941102360449389</v>
       </c>
       <c r="G18">
-        <v>-10.4474477133476</v>
+        <v>-12.48458099364262</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.940843349672401</v>
       </c>
       <c r="E19">
-        <v>-28.97805594428881</v>
+        <v>-31.99135915491776</v>
       </c>
       <c r="F19">
-        <v>-3.692418023999803</v>
+        <v>-4.754443848474368</v>
       </c>
       <c r="G19">
-        <v>-11.14076654763671</v>
+        <v>-12.75156742949152</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.863981816321219</v>
       </c>
       <c r="E20">
-        <v>-29.07058172521353</v>
+        <v>-32.14378985425295</v>
       </c>
       <c r="F20">
-        <v>-3.427097743454941</v>
+        <v>-4.755549718957106</v>
       </c>
       <c r="G20">
-        <v>-11.16115933962866</v>
+        <v>-12.52613110224987</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.868557932229385</v>
       </c>
       <c r="E21">
-        <v>-29.46849647203052</v>
+        <v>-32.45142720749003</v>
       </c>
       <c r="F21">
-        <v>-3.112427474888299</v>
+        <v>-4.04480468878331</v>
       </c>
       <c r="G21">
-        <v>-10.42449556853929</v>
+        <v>-12.0113960325551</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.939866096578446</v>
       </c>
       <c r="E22">
-        <v>-29.46950632173423</v>
+        <v>-32.74763695656875</v>
       </c>
       <c r="F22">
-        <v>-2.951556868529829</v>
+        <v>-3.726805211624816</v>
       </c>
       <c r="G22">
-        <v>-10.43334174186355</v>
+        <v>-12.02132172777242</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.056099611842727</v>
       </c>
       <c r="E23">
-        <v>-30.7976239714148</v>
+        <v>-34.55402712433242</v>
       </c>
       <c r="F23">
-        <v>-2.851134716655848</v>
+        <v>-3.672489989390656</v>
       </c>
       <c r="G23">
-        <v>-10.61317565187204</v>
+        <v>-11.61855506257214</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.196027894781281</v>
       </c>
       <c r="E24">
-        <v>-30.78544916904518</v>
+        <v>-34.46039639574983</v>
       </c>
       <c r="F24">
-        <v>-2.889028383496911</v>
+        <v>-3.280072469866862</v>
       </c>
       <c r="G24">
-        <v>-10.73605083683012</v>
+        <v>-12.75502255579361</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.339278553285334</v>
       </c>
       <c r="E25">
-        <v>-30.05826681289348</v>
+        <v>-34.55950884211871</v>
       </c>
       <c r="F25">
-        <v>-2.832373851717244</v>
+        <v>-3.49551177888475</v>
       </c>
       <c r="G25">
-        <v>-10.86443519278652</v>
+        <v>-12.64399914310824</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.465558064007197</v>
       </c>
       <c r="E26">
-        <v>-32.38078754144438</v>
+        <v>-35.9584269186722</v>
       </c>
       <c r="F26">
-        <v>-2.646612461639455</v>
+        <v>-3.373455983919257</v>
       </c>
       <c r="G26">
-        <v>-11.00484194453672</v>
+        <v>-12.38727308707573</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.56348838444959</v>
       </c>
       <c r="E27">
-        <v>-32.25981162256647</v>
+        <v>-34.53496904147114</v>
       </c>
       <c r="F27">
-        <v>-2.782262594052291</v>
+        <v>-3.268501005617156</v>
       </c>
       <c r="G27">
-        <v>-11.43861943469531</v>
+        <v>-12.82991315666638</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.619018471471197</v>
       </c>
       <c r="E28">
-        <v>-31.72168173504998</v>
+        <v>-35.33742142834134</v>
       </c>
       <c r="F28">
-        <v>-2.852933102287325</v>
+        <v>-3.516566393161705</v>
       </c>
       <c r="G28">
-        <v>-10.93936844953956</v>
+        <v>-13.62464470569324</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.628792638563812</v>
       </c>
       <c r="E29">
-        <v>-31.77670269424317</v>
+        <v>-34.90521481210127</v>
       </c>
       <c r="F29">
-        <v>-3.12057695339704</v>
+        <v>-3.599678979786787</v>
       </c>
       <c r="G29">
-        <v>-11.27591022000556</v>
+        <v>-13.24322894918027</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.587350441392687</v>
       </c>
       <c r="E30">
-        <v>-31.27757655335475</v>
+        <v>-32.70099141005274</v>
       </c>
       <c r="F30">
-        <v>-2.816191694503556</v>
+        <v>-3.073763426362632</v>
       </c>
       <c r="G30">
-        <v>-10.6812544367874</v>
+        <v>-12.76357670039908</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.498353892451272</v>
       </c>
       <c r="E31">
-        <v>-30.52577967673436</v>
+        <v>-34.85724468693802</v>
       </c>
       <c r="F31">
-        <v>-2.936096219323979</v>
+        <v>-3.598590505019509</v>
       </c>
       <c r="G31">
-        <v>-11.22780094950098</v>
+        <v>-13.09164307557704</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.363886573554423</v>
       </c>
       <c r="E32">
-        <v>-30.80023237244322</v>
+        <v>-33.9118510180157</v>
       </c>
       <c r="F32">
-        <v>-3.091909642688357</v>
+        <v>-3.917124279152808</v>
       </c>
       <c r="G32">
-        <v>-10.97449392633341</v>
+        <v>-12.09808918737718</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.192456224856173</v>
       </c>
       <c r="E33">
-        <v>-30.69383813987001</v>
+        <v>-35.35070570684285</v>
       </c>
       <c r="F33">
-        <v>-3.07393738351722</v>
+        <v>-3.623712403244209</v>
       </c>
       <c r="G33">
-        <v>-10.71410602704056</v>
+        <v>-12.44013684761994</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.990361130122794</v>
       </c>
       <c r="E34">
-        <v>-30.6699798745606</v>
+        <v>-34.26123410889249</v>
       </c>
       <c r="F34">
-        <v>-2.986119670044236</v>
+        <v>-3.575739161845882</v>
       </c>
       <c r="G34">
-        <v>-10.7696374207126</v>
+        <v>-12.92726043789198</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.770424131755908</v>
       </c>
       <c r="E35">
-        <v>-30.68671032178194</v>
+        <v>-34.03918265016338</v>
       </c>
       <c r="F35">
-        <v>-3.043241401039081</v>
+        <v>-3.907101861946337</v>
       </c>
       <c r="G35">
-        <v>-10.8425756947575</v>
+        <v>-12.56177173082856</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.542488691607828</v>
       </c>
       <c r="E36">
-        <v>-30.24493277572665</v>
+        <v>-32.32982862343606</v>
       </c>
       <c r="F36">
-        <v>-2.948812487324354</v>
+        <v>-3.9513275692144</v>
       </c>
       <c r="G36">
-        <v>-11.10176266695959</v>
+        <v>-12.04404418707157</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.321234998081665</v>
       </c>
       <c r="E37">
-        <v>-30.13770756817303</v>
+        <v>-33.51006895439616</v>
       </c>
       <c r="F37">
-        <v>-3.14890629020538</v>
+        <v>-3.313921218680056</v>
       </c>
       <c r="G37">
-        <v>-10.43554344152994</v>
+        <v>-13.05998256874996</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.117661049854242</v>
       </c>
       <c r="E38">
-        <v>-28.56646294173165</v>
+        <v>-31.95481889814987</v>
       </c>
       <c r="F38">
-        <v>-3.245988464711274</v>
+        <v>-3.980271554635618</v>
       </c>
       <c r="G38">
-        <v>-10.62575257410939</v>
+        <v>-12.00620842126961</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.942894514708295</v>
       </c>
       <c r="E39">
-        <v>-29.0491892140013</v>
+        <v>-32.33422577169751</v>
       </c>
       <c r="F39">
-        <v>-3.067446296548883</v>
+        <v>-4.21924809503665</v>
       </c>
       <c r="G39">
-        <v>-10.28769816050448</v>
+        <v>-12.3717004095546</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.807456640915602</v>
       </c>
       <c r="E40">
-        <v>-28.81969973671459</v>
+        <v>-31.74564641949857</v>
       </c>
       <c r="F40">
-        <v>-3.022363229018922</v>
+        <v>-3.783871442003674</v>
       </c>
       <c r="G40">
-        <v>-10.22703165509191</v>
+        <v>-12.41038601174045</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.716785499066789</v>
       </c>
       <c r="E41">
-        <v>-28.42026115839401</v>
+        <v>-31.53806796369797</v>
       </c>
       <c r="F41">
-        <v>-3.155574647797916</v>
+        <v>-3.843198287024772</v>
       </c>
       <c r="G41">
-        <v>-9.85136131752952</v>
+        <v>-12.82363617982316</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.679706551109256</v>
       </c>
       <c r="E42">
-        <v>-27.51073979632346</v>
+        <v>-31.56568486243375</v>
       </c>
       <c r="F42">
-        <v>-3.353274468884852</v>
+        <v>-3.886539297906645</v>
       </c>
       <c r="G42">
-        <v>-10.40829617770031</v>
+        <v>-11.66023970126332</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.69757006917689</v>
       </c>
       <c r="E43">
-        <v>-27.34008878181841</v>
+        <v>-31.57428669881132</v>
       </c>
       <c r="F43">
-        <v>-3.346528244756453</v>
+        <v>-4.494348081138963</v>
       </c>
       <c r="G43">
-        <v>-10.1382122686993</v>
+        <v>-12.4805450911245</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.775904039532376</v>
       </c>
       <c r="E44">
-        <v>-27.32948309569245</v>
+        <v>-28.49516211848088</v>
       </c>
       <c r="F44">
-        <v>-3.562325408492349</v>
+        <v>-4.558679093640372</v>
       </c>
       <c r="G44">
-        <v>-10.87108622888751</v>
+        <v>-12.16350362038627</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.91136068070218</v>
       </c>
       <c r="E45">
-        <v>-25.9223865950811</v>
+        <v>-31.62975371269427</v>
       </c>
       <c r="F45">
-        <v>-3.720500507322109</v>
+        <v>-4.013681268725327</v>
       </c>
       <c r="G45">
-        <v>-10.18403124655538</v>
+        <v>-11.83262851955343</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.101825347079425</v>
       </c>
       <c r="E46">
-        <v>-26.47610122589498</v>
+        <v>-30.32244666531595</v>
       </c>
       <c r="F46">
-        <v>-3.798335565223956</v>
+        <v>-4.691622121380859</v>
       </c>
       <c r="G46">
-        <v>-10.46328288859348</v>
+        <v>-11.6367625610055</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.336393969005278</v>
       </c>
       <c r="E47">
-        <v>-25.52684250440712</v>
+        <v>-30.51428414546588</v>
       </c>
       <c r="F47">
-        <v>-3.437145840050899</v>
+        <v>-4.434173816264801</v>
       </c>
       <c r="G47">
-        <v>-10.12004086370309</v>
+        <v>-12.61944576217891</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.607503755778302</v>
       </c>
       <c r="E48">
-        <v>-25.17151126292126</v>
+        <v>-28.85457351504765</v>
       </c>
       <c r="F48">
-        <v>-3.373107241242678</v>
+        <v>-4.069490037386736</v>
       </c>
       <c r="G48">
-        <v>-10.42360963871824</v>
+        <v>-12.55626255983025</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.898970343085038</v>
       </c>
       <c r="E49">
-        <v>-25.47683003746641</v>
+        <v>-29.51892782281694</v>
       </c>
       <c r="F49">
-        <v>-3.506519953300552</v>
+        <v>-4.434508476695532</v>
       </c>
       <c r="G49">
-        <v>-11.28635434822928</v>
+        <v>-12.24707305228377</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.20324874054814</v>
       </c>
       <c r="E50">
-        <v>-24.43086122507074</v>
+        <v>-27.82756089484809</v>
       </c>
       <c r="F50">
-        <v>-3.508360585669573</v>
+        <v>-4.06655927351563</v>
       </c>
       <c r="G50">
-        <v>-10.44947550827134</v>
+        <v>-11.74918705529675</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.504542609978239</v>
       </c>
       <c r="E51">
-        <v>-23.52248103845012</v>
+        <v>-29.03350258003872</v>
       </c>
       <c r="F51">
-        <v>-3.609217630430024</v>
+        <v>-4.760614357257822</v>
       </c>
       <c r="G51">
-        <v>-10.71122839573292</v>
+        <v>-12.4573895105795</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.799922388378613</v>
       </c>
       <c r="E52">
-        <v>-23.55113269349665</v>
+        <v>-28.15140112808462</v>
       </c>
       <c r="F52">
-        <v>-3.738886121827244</v>
+        <v>-3.880352221775135</v>
       </c>
       <c r="G52">
-        <v>-10.68711797971412</v>
+        <v>-12.01931690139959</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.079442853505498</v>
       </c>
       <c r="E53">
-        <v>-23.00329602194472</v>
+        <v>-26.34439055938189</v>
       </c>
       <c r="F53">
-        <v>-3.647175081561103</v>
+        <v>-4.02122769576483</v>
       </c>
       <c r="G53">
-        <v>-10.73587693208747</v>
+        <v>-13.29846503291196</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.341422006075202</v>
       </c>
       <c r="E54">
-        <v>-23.8598115957555</v>
+        <v>-26.59668543177123</v>
       </c>
       <c r="F54">
-        <v>-3.561582362932038</v>
+        <v>-4.619760420820599</v>
       </c>
       <c r="G54">
-        <v>-10.88527751213211</v>
+        <v>-12.18754513075233</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.582113213724289</v>
       </c>
       <c r="E55">
-        <v>-22.73156946758847</v>
+        <v>-25.82606595293795</v>
       </c>
       <c r="F55">
-        <v>-3.790543113065822</v>
+        <v>-4.603632107488093</v>
       </c>
       <c r="G55">
-        <v>-10.40913945164109</v>
+        <v>-12.95163007041398</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.801167791274461</v>
       </c>
       <c r="E56">
-        <v>-22.07357766579996</v>
+        <v>-26.18506525837002</v>
       </c>
       <c r="F56">
-        <v>-3.655254977208009</v>
+        <v>-4.465309661833826</v>
       </c>
       <c r="G56">
-        <v>-11.26616827319557</v>
+        <v>-12.62742897423304</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.00145641050502</v>
       </c>
       <c r="E57">
-        <v>-22.14336145025816</v>
+        <v>-24.81953109220107</v>
       </c>
       <c r="F57">
-        <v>-3.836185328592671</v>
+        <v>-4.392059617506474</v>
       </c>
       <c r="G57">
-        <v>-11.47744284818666</v>
+        <v>-12.02391061158282</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.18345761845992</v>
       </c>
       <c r="E58">
-        <v>-21.66097481353909</v>
+        <v>-24.8740992039935</v>
       </c>
       <c r="F58">
-        <v>-3.577542517681776</v>
+        <v>-4.094859617464873</v>
       </c>
       <c r="G58">
-        <v>-11.66362264069111</v>
+        <v>-13.42906093219942</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.35086078888396</v>
       </c>
       <c r="E59">
-        <v>-20.94288563319479</v>
+        <v>-24.34398697970759</v>
       </c>
       <c r="F59">
-        <v>-3.698761661570442</v>
+        <v>-4.266069077377684</v>
       </c>
       <c r="G59">
-        <v>-11.37409421272883</v>
+        <v>-13.93896768436947</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.50265947385912</v>
       </c>
       <c r="E60">
-        <v>-21.19535711607043</v>
+        <v>-23.47754951934602</v>
       </c>
       <c r="F60">
-        <v>-3.612857476797925</v>
+        <v>-4.482924894654357</v>
       </c>
       <c r="G60">
-        <v>-10.84787814879756</v>
+        <v>-13.41857414809544</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.64228282960818</v>
       </c>
       <c r="E61">
-        <v>-20.65530941981169</v>
+        <v>-22.94030042002402</v>
       </c>
       <c r="F61">
-        <v>-4.089516647716816</v>
+        <v>-4.624082841928407</v>
       </c>
       <c r="G61">
-        <v>-11.19997619067689</v>
+        <v>-13.73239345926229</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.76660617480306</v>
       </c>
       <c r="E62">
-        <v>-20.27176125678404</v>
+        <v>-22.80761613159928</v>
       </c>
       <c r="F62">
-        <v>-3.840238530294569</v>
+        <v>-4.395701948976583</v>
       </c>
       <c r="G62">
-        <v>-11.83048916309667</v>
+        <v>-14.41275639022393</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.8789719368645</v>
       </c>
       <c r="E63">
-        <v>-19.47488115718027</v>
+        <v>-23.50200780746145</v>
       </c>
       <c r="F63">
-        <v>-3.878839622897623</v>
+        <v>-4.113626280975295</v>
       </c>
       <c r="G63">
-        <v>-11.83554880674133</v>
+        <v>-13.37700763338039</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.97422029246813</v>
       </c>
       <c r="E64">
-        <v>-20.40513840173195</v>
+        <v>-24.07025431136595</v>
       </c>
       <c r="F64">
-        <v>-4.018346633937893</v>
+        <v>-4.579729566080314</v>
       </c>
       <c r="G64">
-        <v>-11.67240647080574</v>
+        <v>-13.29907862134358</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.05630323062023</v>
       </c>
       <c r="E65">
-        <v>-19.42885374736631</v>
+        <v>-24.10993732909516</v>
       </c>
       <c r="F65">
-        <v>-4.305818287201017</v>
+        <v>-4.45523257237877</v>
       </c>
       <c r="G65">
-        <v>-11.81657350246306</v>
+        <v>-14.07944826360476</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.1207021199166</v>
       </c>
       <c r="E66">
-        <v>-19.67148938469729</v>
+        <v>-23.20309682363715</v>
       </c>
       <c r="F66">
-        <v>-4.212583879281127</v>
+        <v>-4.545097181704072</v>
       </c>
       <c r="G66">
-        <v>-12.08220151258635</v>
+        <v>-13.37664013656573</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.17118142720106</v>
       </c>
       <c r="E67">
-        <v>-19.90231023334226</v>
+        <v>-23.00882528870809</v>
       </c>
       <c r="F67">
-        <v>-3.918778528856199</v>
+        <v>-4.087003381016722</v>
       </c>
       <c r="G67">
-        <v>-12.14685142097209</v>
+        <v>-14.14164545887481</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.20772289475446</v>
       </c>
       <c r="E68">
-        <v>-19.65774999455802</v>
+        <v>-22.66851499550567</v>
       </c>
       <c r="F68">
-        <v>-4.175055522464699</v>
+        <v>-4.351172230871693</v>
       </c>
       <c r="G68">
-        <v>-11.88900974960937</v>
+        <v>-14.1328435820416</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.2329375395258</v>
       </c>
       <c r="E69">
-        <v>-19.58338339440406</v>
+        <v>-23.26810306801726</v>
       </c>
       <c r="F69">
-        <v>-4.158625683397573</v>
+        <v>-4.251842695602004</v>
       </c>
       <c r="G69">
-        <v>-12.08360915663535</v>
+        <v>-13.63928879751305</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.25212262183711</v>
       </c>
       <c r="E70">
-        <v>-18.99757999677182</v>
+        <v>-22.83027208705965</v>
       </c>
       <c r="F70">
-        <v>-4.060773955574479</v>
+        <v>-4.442675350919732</v>
       </c>
       <c r="G70">
-        <v>-11.77544995265855</v>
+        <v>-13.02347241645802</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.26563651213275</v>
       </c>
       <c r="E71">
-        <v>-18.85230202213175</v>
+        <v>-22.33991533608708</v>
       </c>
       <c r="F71">
-        <v>-4.521960051776478</v>
+        <v>-4.371463090403267</v>
       </c>
       <c r="G71">
-        <v>-11.62835935259176</v>
+        <v>-13.87755798227368</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.28064002063572</v>
       </c>
       <c r="E72">
-        <v>-18.28782320860163</v>
+        <v>-23.2261512848102</v>
       </c>
       <c r="F72">
-        <v>-4.299371103705029</v>
+        <v>-4.433935246452795</v>
       </c>
       <c r="G72">
-        <v>-12.14586705450426</v>
+        <v>-13.97583713042217</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.29591276325775</v>
       </c>
       <c r="E73">
-        <v>-19.74813380727711</v>
+        <v>-23.48268028039671</v>
       </c>
       <c r="F73">
-        <v>-4.143922990365285</v>
+        <v>-4.62406296111074</v>
       </c>
       <c r="G73">
-        <v>-11.3526153364007</v>
+        <v>-12.70445565034101</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.31504654528981</v>
       </c>
       <c r="E74">
-        <v>-19.2447622220065</v>
+        <v>-23.25167376431743</v>
       </c>
       <c r="F74">
-        <v>-4.488169288681481</v>
+        <v>-4.949229473038256</v>
       </c>
       <c r="G74">
-        <v>-11.40891453591765</v>
+        <v>-14.03055149992591</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.332554305991</v>
       </c>
       <c r="E75">
-        <v>-18.48482994183132</v>
+        <v>-23.23936537196458</v>
       </c>
       <c r="F75">
-        <v>-4.637256368735128</v>
+        <v>-4.686923621472181</v>
       </c>
       <c r="G75">
-        <v>-11.75947368488561</v>
+        <v>-12.59757313926366</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.34660614559526</v>
       </c>
       <c r="E76">
-        <v>-19.06130468300776</v>
+        <v>-24.26872374170011</v>
       </c>
       <c r="F76">
-        <v>-4.462455936131182</v>
+        <v>-4.597851759751358</v>
       </c>
       <c r="G76">
-        <v>-11.42076302696881</v>
+        <v>-12.42134201052744</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.34708982904887</v>
       </c>
       <c r="E77">
-        <v>-19.85792665959308</v>
+        <v>-23.08800565673221</v>
       </c>
       <c r="F77">
-        <v>-4.251189942088598</v>
+        <v>-4.980808495167778</v>
       </c>
       <c r="G77">
-        <v>-10.95032444832654</v>
+        <v>-12.70519064397032</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.33125941886567</v>
       </c>
       <c r="E78">
-        <v>-20.80487585933703</v>
+        <v>-24.16043434275469</v>
       </c>
       <c r="F78">
-        <v>-4.597092975210393</v>
+        <v>-5.101410505341358</v>
       </c>
       <c r="G78">
-        <v>-11.34517024468232</v>
+        <v>-11.9188623033572</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.29138458519191</v>
       </c>
       <c r="E79">
-        <v>-20.63817367416667</v>
+        <v>-24.57824494012438</v>
       </c>
       <c r="F79">
-        <v>-4.400632391758046</v>
+        <v>-5.051158425217928</v>
       </c>
       <c r="G79">
-        <v>-11.05827991885383</v>
+        <v>-12.09402047264347</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-11.22836384536734</v>
       </c>
       <c r="E80">
-        <v>-21.45186799776091</v>
+        <v>-27.00995849818523</v>
       </c>
       <c r="F80">
-        <v>-4.767226385866968</v>
+        <v>-5.085303729561324</v>
       </c>
       <c r="G80">
-        <v>-10.90904996233029</v>
+        <v>-12.52405080778118</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-11.13992571704759</v>
       </c>
       <c r="E81">
-        <v>-21.7638843853634</v>
+        <v>-25.85016649160677</v>
       </c>
       <c r="F81">
-        <v>-4.787236428848992</v>
+        <v>-4.752757292442269</v>
       </c>
       <c r="G81">
-        <v>-10.58741478140884</v>
+        <v>-12.11985024875942</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-11.0284649475961</v>
       </c>
       <c r="E82">
-        <v>-22.03209231541569</v>
+        <v>-26.67036823235003</v>
       </c>
       <c r="F82">
-        <v>-4.788413538928371</v>
+        <v>-5.846367109250773</v>
       </c>
       <c r="G82">
-        <v>-10.16868497332186</v>
+        <v>-11.12669338836825</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.8984966905332</v>
       </c>
       <c r="E83">
-        <v>-23.00704106994907</v>
+        <v>-27.35382817195768</v>
       </c>
       <c r="F83">
-        <v>-4.968956214368522</v>
+        <v>-5.215731005499509</v>
       </c>
       <c r="G83">
-        <v>-10.99965105202967</v>
+        <v>-12.81444547823516</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.75220149680264</v>
       </c>
       <c r="E84">
-        <v>-23.09833963441771</v>
+        <v>-27.37506218657965</v>
       </c>
       <c r="F84">
-        <v>-5.076555341420359</v>
+        <v>-5.150540976001396</v>
       </c>
       <c r="G84">
-        <v>-9.572349204665258</v>
+        <v>-11.94433442632316</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.59973086171065</v>
       </c>
       <c r="E85">
-        <v>-24.23437073787793</v>
+        <v>-29.12554381424463</v>
       </c>
       <c r="F85">
-        <v>-5.102865118500674</v>
+        <v>-5.133742513440025</v>
       </c>
       <c r="G85">
-        <v>-10.18312234818342</v>
+        <v>-12.21510739185166</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.44617754193297</v>
       </c>
       <c r="E86">
-        <v>-25.74069516094535</v>
+        <v>-29.49778437767513</v>
       </c>
       <c r="F86">
-        <v>-5.285350315500391</v>
+        <v>-5.810866595836397</v>
       </c>
       <c r="G86">
-        <v>-10.02282811256142</v>
+        <v>-10.9137092969447</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.30787195364334</v>
       </c>
       <c r="E87">
-        <v>-26.20903447129263</v>
+        <v>-29.84522701743963</v>
       </c>
       <c r="F87">
-        <v>-5.281515802792832</v>
+        <v>-5.602350781571109</v>
       </c>
       <c r="G87">
-        <v>-10.60926443577318</v>
+        <v>-11.87923499058378</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.19373817613127</v>
       </c>
       <c r="E88">
-        <v>-27.78980247857214</v>
+        <v>-31.37427305884054</v>
       </c>
       <c r="F88">
-        <v>-5.182713109191324</v>
+        <v>-5.539062683629823</v>
       </c>
       <c r="G88">
-        <v>-9.906754899896066</v>
+        <v>-11.18811129351794</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.11922034367631</v>
       </c>
       <c r="E89">
-        <v>-29.32308490740722</v>
+        <v>-32.60034381099526</v>
       </c>
       <c r="F89">
-        <v>-5.344885909106994</v>
+        <v>-5.557058965455643</v>
       </c>
       <c r="G89">
-        <v>-10.10476349612232</v>
+        <v>-11.74472787519746</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.09012099340788</v>
       </c>
       <c r="E90">
-        <v>-30.42955866101937</v>
+        <v>-35.14355292759897</v>
       </c>
       <c r="F90">
-        <v>-5.307616002920239</v>
+        <v>-5.861618181503714</v>
       </c>
       <c r="G90">
-        <v>-10.35284025212414</v>
+        <v>-11.65336226087473</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-10.11842761093201</v>
       </c>
       <c r="E91">
-        <v>-32.58980831621642</v>
+        <v>-35.33695952399256</v>
       </c>
       <c r="F91">
-        <v>-5.603900656981747</v>
+        <v>-5.938399556069201</v>
       </c>
       <c r="G91">
-        <v>-10.45704528640898</v>
+        <v>-11.75802666617789</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-10.20607508467206</v>
       </c>
       <c r="E92">
-        <v>-33.72420011208586</v>
+        <v>-37.580098367426</v>
       </c>
       <c r="F92">
-        <v>-5.469478993427262</v>
+        <v>-6.016203964377144</v>
       </c>
       <c r="G92">
-        <v>-10.8509329660694</v>
+        <v>-12.18075300212428</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-10.36300582766274</v>
       </c>
       <c r="E93">
-        <v>-35.83851971966011</v>
+        <v>-38.77408714547339</v>
       </c>
       <c r="F93">
-        <v>-5.461684056166919</v>
+        <v>-5.832071972980662</v>
       </c>
       <c r="G93">
-        <v>-10.98835708742206</v>
+        <v>-12.96230060292529</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.58354531878947</v>
       </c>
       <c r="E94">
-        <v>-37.04958310895341</v>
+        <v>-39.71870418110338</v>
       </c>
       <c r="F94">
-        <v>-5.221735840802403</v>
+        <v>-5.57516707688084</v>
       </c>
       <c r="G94">
-        <v>-11.03606276767483</v>
+        <v>-12.88534611369164</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.87036575487274</v>
       </c>
       <c r="E95">
-        <v>-39.26145283936389</v>
+        <v>-41.52989000284119</v>
       </c>
       <c r="F95">
-        <v>-5.336373605675827</v>
+        <v>-6.113563641962976</v>
       </c>
       <c r="G95">
-        <v>-11.88299198926935</v>
+        <v>-12.84565973893015</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.21808136868077</v>
       </c>
       <c r="E96">
-        <v>-40.92946869111218</v>
+        <v>-44.87644135145759</v>
       </c>
       <c r="F96">
-        <v>-4.982345116699971</v>
+        <v>-6.315627302527859</v>
       </c>
       <c r="G96">
-        <v>-12.12898188835936</v>
+        <v>-12.88481455579901</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.61725300571505</v>
       </c>
       <c r="E97">
-        <v>-43.68304806774222</v>
+        <v>-46.70511387557601</v>
       </c>
       <c r="F97">
-        <v>-5.187566513804327</v>
+        <v>-5.685647265759613</v>
       </c>
       <c r="G97">
-        <v>-11.96634157932236</v>
+        <v>-13.97368628968996</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.07106914020202</v>
       </c>
       <c r="E98">
-        <v>-45.37428366996484</v>
+        <v>-48.29811102691324</v>
       </c>
       <c r="F98">
-        <v>-5.39021334502078</v>
+        <v>-5.450177204574631</v>
       </c>
       <c r="G98">
-        <v>-12.29963822166608</v>
+        <v>-14.22042922912786</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.55303464283769</v>
       </c>
       <c r="E99">
-        <v>-47.99678183796885</v>
+        <v>-51.91530209612406</v>
       </c>
       <c r="F99">
-        <v>-4.944090281671287</v>
+        <v>-5.784702611418975</v>
       </c>
       <c r="G99">
-        <v>-12.70701500315737</v>
+        <v>-13.94096430768839</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.08364244444238</v>
       </c>
       <c r="E100">
-        <v>-49.6190204780921</v>
+        <v>-53.08607565217113</v>
       </c>
       <c r="F100">
-        <v>-4.821069438681532</v>
+        <v>-5.064187816096562</v>
       </c>
       <c r="G100">
-        <v>-13.16293745762066</v>
+        <v>-13.91761513507138</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.60301631458936</v>
       </c>
       <c r="E101">
-        <v>-52.0953372408915</v>
+        <v>-55.74043163481909</v>
       </c>
       <c r="F101">
-        <v>-4.864943918170808</v>
+        <v>-5.443989300075718</v>
       </c>
       <c r="G101">
-        <v>-13.60769391511715</v>
+        <v>-15.43466823575129</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.17633632415751</v>
       </c>
       <c r="E102">
-        <v>-54.32778662142984</v>
+        <v>-56.43824004432004</v>
       </c>
       <c r="F102">
-        <v>-4.952870976140962</v>
+        <v>-5.867867385190434</v>
       </c>
       <c r="G102">
-        <v>-13.79986849941071</v>
+        <v>-16.65528593708629</v>
       </c>
     </row>
   </sheetData>
